--- a/output/pdf_financials_xlsx/VRDN.xlsx
+++ b/output/pdf_financials_xlsx/VRDN.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.099227</v>
+        <v>1.26186</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.794382</v>
+        <v>1.514815</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.39469</v>
+        <v>1.94836</v>
       </c>
     </row>
     <row r="11">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002704</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.013708</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.02581</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.162633</v>
+        <v>-1.165337</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.309197</v>
+        <v>-2.322905</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.55367</v>
+        <v>-1.57948</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.162633</v>
+        <v>-1.165337</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.309197</v>
+        <v>-2.322905</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.55367</v>
+        <v>-1.57948</v>
       </c>
     </row>
     <row r="30">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.079498</v>
+        <v>0.119352</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.116389</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.079498</v>
+        <v>0.119352</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.116389</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">

--- a/output/pdf_financials_xlsx/VRDN.xlsx
+++ b/output/pdf_financials_xlsx/VRDN.xlsx
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0.16</v>
+        <v>1.467884</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.383194</v>
+        <v>3.154734</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>4.552491</v>
       </c>
     </row>
     <row r="89">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
+        <v>-0.046333</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>-0.060592</v>
+        <v>0.077461</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-0.069123</v>
       </c>
     </row>
     <row r="129">
@@ -2960,7 +2960,11 @@
           <t>Share capital Note 10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3144,7 +3148,11 @@
           <t>Share capital Note 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>1.467884</v>
       </c>
@@ -4126,7 +4134,11 @@
           <t>Share issue costs Note 10</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4542,7 +4554,11 @@
           <t>Share issue costs Note 9</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>-0.046333</v>
       </c>
